--- a/PasseD_26_27.xlsx
+++ b/PasseD_26_27.xlsx
@@ -445,48 +445,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5836,7 +5832,7 @@
         <v>2</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>16</v>
+        <v>87</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5874,7 +5870,7 @@
         <v>3</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6785,7 +6781,7 @@
       <c r="K158" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L158" s="8" t="s">
+      <c r="L158" s="2" t="s">
         <v>99</v>
       </c>
     </row>
@@ -9951,7 +9947,7 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="10"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -10581,7 +10577,7 @@
       <c r="K6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>24</v>
       </c>
       <c r="M6" s="1"/>
@@ -10678,7 +10674,7 @@
       <c r="K8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>57</v>
       </c>
       <c r="M8" s="1"/>
@@ -10874,7 +10870,7 @@
       <c r="K12" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>84</v>
       </c>
       <c r="M12" s="1"/>
@@ -11228,7 +11224,7 @@
       <c r="K5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>75</v>
       </c>
       <c r="M5" s="1"/>
@@ -11521,7 +11517,7 @@
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>27</v>
       </c>
       <c r="M2" s="1"/>
@@ -11717,7 +11713,7 @@
       <c r="K6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>66</v>
       </c>
       <c r="M6" s="1"/>
@@ -11766,7 +11762,7 @@
       <c r="K7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>67</v>
       </c>
       <c r="M7" s="1"/>
@@ -11815,7 +11811,7 @@
       <c r="K8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>68</v>
       </c>
       <c r="M8" s="1"/>
@@ -12011,7 +12007,7 @@
       <c r="K12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>67</v>
       </c>
       <c r="M12" s="1"/>
@@ -12060,7 +12056,7 @@
       <c r="K13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>71</v>
       </c>
       <c r="M13" s="1"/>
@@ -12458,7 +12454,7 @@
       <c r="K5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>49</v>
       </c>
       <c r="M5" s="1"/>
@@ -12556,7 +12552,7 @@
       <c r="K7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>16</v>
       </c>
       <c r="M7" s="1"/>
@@ -12948,7 +12944,7 @@
       <c r="K15" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="8" t="s">
         <v>83</v>
       </c>
       <c r="M15" s="1"/>
@@ -13346,7 +13342,7 @@
       <c r="K3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="N3" s="1"/>
@@ -13661,7 +13657,7 @@
       <c r="K10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>61</v>
       </c>
       <c r="M10" s="1"/>
@@ -13857,7 +13853,7 @@
       <c r="K14" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L14" s="9" t="s">
+      <c r="L14" s="8" t="s">
         <v>61</v>
       </c>
       <c r="M14" s="1"/>
@@ -14691,7 +14687,7 @@
       <c r="K3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>41</v>
       </c>
       <c r="M3" s="1"/>
@@ -14936,7 +14932,7 @@
       <c r="K8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>43</v>
       </c>
       <c r="M8" s="1"/>
@@ -14985,7 +14981,7 @@
       <c r="K9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>72</v>
       </c>
       <c r="M9" s="1"/>
@@ -15297,7 +15293,7 @@
       <c r="K3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>18</v>
       </c>
       <c r="M3" s="1"/>
@@ -15346,7 +15342,7 @@
       <c r="K4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="8" t="s">
         <v>56</v>
       </c>
       <c r="M4" s="1"/>
@@ -15534,7 +15530,7 @@
       <c r="K2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -15572,7 +15568,7 @@
       <c r="K3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>46</v>
       </c>
     </row>
@@ -15610,7 +15606,7 @@
       <c r="K4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -15648,7 +15644,7 @@
       <c r="K5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>51</v>
       </c>
       <c r="M5" s="1"/>
@@ -15746,7 +15742,7 @@
       <c r="K7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>51</v>
       </c>
       <c r="M7" s="1"/>
@@ -15795,7 +15791,7 @@
       <c r="K8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>55</v>
       </c>
       <c r="M8" s="1"/>
@@ -15844,7 +15840,7 @@
       <c r="K9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>51</v>
       </c>
       <c r="M9" s="1"/>

--- a/PasseD_26_27.xlsx
+++ b/PasseD_26_27.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="104">
   <si>
     <t xml:space="preserve">journee</t>
   </si>
@@ -347,9 +347,6 @@
   </si>
   <si>
     <t xml:space="preserve">JAMAL ZAHRY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABLO MARIA DEL MORAL JIMENEZ </t>
   </si>
   <si>
     <t xml:space="preserve">GABRIEL PEREIRA DA SILVA </t>
@@ -675,10 +672,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W167"/>
+  <dimension ref="A1:W806"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.42"/>
@@ -742,7 +739,7 @@
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -791,7 +788,7 @@
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -840,7 +837,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
@@ -889,7 +886,7 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>1</v>
       </c>
@@ -938,7 +935,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>1</v>
       </c>
@@ -976,7 +973,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>1</v>
       </c>
@@ -1014,7 +1011,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>1</v>
       </c>
@@ -1052,7 +1049,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>1</v>
       </c>
@@ -1090,7 +1087,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>1</v>
       </c>
@@ -1128,7 +1125,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>1</v>
       </c>
@@ -1166,7 +1163,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1</v>
       </c>
@@ -1204,7 +1201,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>1</v>
       </c>
@@ -1242,7 +1239,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>1</v>
       </c>
@@ -1280,7 +1277,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>1</v>
       </c>
@@ -1318,7 +1315,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>1</v>
       </c>
@@ -1356,7 +1353,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>1</v>
       </c>
@@ -1394,7 +1391,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>1</v>
       </c>
@@ -1432,7 +1429,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>1</v>
       </c>
@@ -1470,7 +1467,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>1</v>
       </c>
@@ -1508,7 +1505,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>1</v>
       </c>
@@ -1546,7 +1543,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>1</v>
       </c>
@@ -1584,7 +1581,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>1</v>
       </c>
@@ -1622,7 +1619,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>1</v>
       </c>
@@ -1660,7 +1657,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>1</v>
       </c>
@@ -1698,7 +1695,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>1</v>
       </c>
@@ -1736,7 +1733,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>1</v>
       </c>
@@ -1774,7 +1771,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>1</v>
       </c>
@@ -1812,7 +1809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>1</v>
       </c>
@@ -1850,7 +1847,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>1</v>
       </c>
@@ -1888,7 +1885,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>1</v>
       </c>
@@ -1926,7 +1923,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>1</v>
       </c>
@@ -1964,7 +1961,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>1</v>
       </c>
@@ -2002,7 +1999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>1</v>
       </c>
@@ -2040,7 +2037,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>1</v>
       </c>
@@ -2154,7 +2151,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>1</v>
       </c>
@@ -2192,7 +2189,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>1</v>
       </c>
@@ -2230,7 +2227,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>1</v>
       </c>
@@ -2268,7 +2265,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>1</v>
       </c>
@@ -2306,7 +2303,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>1</v>
       </c>
@@ -2344,7 +2341,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>1</v>
       </c>
@@ -2382,7 +2379,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
         <v>1</v>
       </c>
@@ -2420,7 +2417,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>1</v>
       </c>
@@ -2458,7 +2455,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>1</v>
       </c>
@@ -2496,7 +2493,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>2</v>
       </c>
@@ -2534,7 +2531,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
         <v>2</v>
       </c>
@@ -2572,7 +2569,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
         <v>2</v>
       </c>
@@ -2610,7 +2607,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
         <v>2</v>
       </c>
@@ -2648,7 +2645,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
         <v>2</v>
       </c>
@@ -2686,7 +2683,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
         <v>2</v>
       </c>
@@ -2724,7 +2721,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
         <v>2</v>
       </c>
@@ -2762,7 +2759,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
         <v>2</v>
       </c>
@@ -2800,7 +2797,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
         <v>2</v>
       </c>
@@ -2838,7 +2835,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
         <v>2</v>
       </c>
@@ -2876,7 +2873,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
         <v>2</v>
       </c>
@@ -2914,7 +2911,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
         <v>2</v>
       </c>
@@ -2952,7 +2949,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="n">
         <v>2</v>
       </c>
@@ -2990,7 +2987,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
         <v>2</v>
       </c>
@@ -3028,7 +3025,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
         <v>2</v>
       </c>
@@ -3066,7 +3063,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
         <v>2</v>
       </c>
@@ -3104,7 +3101,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
         <v>2</v>
       </c>
@@ -3142,7 +3139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
         <v>2</v>
       </c>
@@ -3180,7 +3177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="n">
         <v>2</v>
       </c>
@@ -3218,7 +3215,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" s="6" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" s="6" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
         <v>2</v>
       </c>
@@ -3267,7 +3264,7 @@
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
         <v>2</v>
       </c>
@@ -3305,7 +3302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
         <v>2</v>
       </c>
@@ -3343,7 +3340,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
         <v>2</v>
       </c>
@@ -3381,7 +3378,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
         <v>2</v>
       </c>
@@ -3419,7 +3416,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
         <v>2</v>
       </c>
@@ -3457,7 +3454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="n">
         <v>2</v>
       </c>
@@ -3495,7 +3492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="n">
         <v>2</v>
       </c>
@@ -3533,7 +3530,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
         <v>2</v>
       </c>
@@ -3571,7 +3568,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
         <v>2</v>
       </c>
@@ -3609,7 +3606,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
         <v>3</v>
       </c>
@@ -3647,7 +3644,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
         <v>3</v>
       </c>
@@ -3685,7 +3682,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
         <v>3</v>
       </c>
@@ -3723,7 +3720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="n">
         <v>3</v>
       </c>
@@ -3761,7 +3758,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
         <v>3</v>
       </c>
@@ -3799,7 +3796,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
         <v>3</v>
       </c>
@@ -3837,7 +3834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
         <v>3</v>
       </c>
@@ -3875,7 +3872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="n">
         <v>3</v>
       </c>
@@ -3913,7 +3910,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="n">
         <v>3</v>
       </c>
@@ -3951,7 +3948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
         <v>3</v>
       </c>
@@ -3989,7 +3986,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
         <v>3</v>
       </c>
@@ -4027,7 +4024,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
         <v>3</v>
       </c>
@@ -4065,7 +4062,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="n">
         <v>3</v>
       </c>
@@ -4103,7 +4100,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="n">
         <v>3</v>
       </c>
@@ -4141,7 +4138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="n">
         <v>3</v>
       </c>
@@ -4179,7 +4176,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="n">
         <v>3</v>
       </c>
@@ -4217,7 +4214,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="n">
         <v>3</v>
       </c>
@@ -4255,7 +4252,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="n">
         <v>3</v>
       </c>
@@ -4293,7 +4290,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="n">
         <v>3</v>
       </c>
@@ -4331,7 +4328,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="n">
         <v>3</v>
       </c>
@@ -4369,7 +4366,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="n">
         <v>3</v>
       </c>
@@ -4407,7 +4404,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="n">
         <v>3</v>
       </c>
@@ -4445,7 +4442,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="n">
         <v>3</v>
       </c>
@@ -4483,7 +4480,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="n">
         <v>3</v>
       </c>
@@ -4559,7 +4556,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="n">
         <v>3</v>
       </c>
@@ -4597,7 +4594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="n">
         <v>3</v>
       </c>
@@ -4635,7 +4632,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="n">
         <v>3</v>
       </c>
@@ -4673,7 +4670,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="n">
         <v>3</v>
       </c>
@@ -4711,7 +4708,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="n">
         <v>3</v>
       </c>
@@ -4749,7 +4746,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
         <v>3</v>
       </c>
@@ -4787,7 +4784,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="n">
         <v>3</v>
       </c>
@@ -4825,7 +4822,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="n">
         <v>3</v>
       </c>
@@ -4863,7 +4860,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="n">
         <v>3</v>
       </c>
@@ -4901,7 +4898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="n">
         <v>3</v>
       </c>
@@ -4939,7 +4936,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="n">
         <v>3</v>
       </c>
@@ -4977,7 +4974,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="n">
         <v>3</v>
       </c>
@@ -5015,7 +5012,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="n">
         <v>3</v>
       </c>
@@ -5053,7 +5050,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="n">
         <v>3</v>
       </c>
@@ -5091,7 +5088,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="n">
         <v>3</v>
       </c>
@@ -5129,7 +5126,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="n">
         <v>3</v>
       </c>
@@ -5167,7 +5164,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="n">
         <v>3</v>
       </c>
@@ -5205,7 +5202,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="n">
         <v>3</v>
       </c>
@@ -5243,7 +5240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="n">
         <v>3</v>
       </c>
@@ -5281,7 +5278,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="n">
         <v>3</v>
       </c>
@@ -5319,7 +5316,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="n">
         <v>3</v>
       </c>
@@ -5357,7 +5354,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="n">
         <v>3</v>
       </c>
@@ -5395,7 +5392,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="n">
         <v>3</v>
       </c>
@@ -5433,7 +5430,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="n">
         <v>3</v>
       </c>
@@ -5471,7 +5468,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="n">
         <v>3</v>
       </c>
@@ -5509,7 +5506,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="n">
         <v>3</v>
       </c>
@@ -5547,7 +5544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="n">
         <v>3</v>
       </c>
@@ -5585,7 +5582,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" s="6" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="128" s="6" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="n">
         <v>3</v>
       </c>
@@ -5634,7 +5631,7 @@
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
     </row>
-    <row r="129" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="n">
         <v>4</v>
       </c>
@@ -5672,7 +5669,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="130" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="n">
         <v>4</v>
       </c>
@@ -5710,7 +5707,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="131" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="n">
         <v>4</v>
       </c>
@@ -5748,7 +5745,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="n">
         <v>4</v>
       </c>
@@ -5797,7 +5794,7 @@
       <c r="V132" s="4"/>
       <c r="W132" s="4"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="n">
         <v>4</v>
       </c>
@@ -5835,7 +5832,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="n">
         <v>4</v>
       </c>
@@ -5873,7 +5870,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="n">
         <v>4</v>
       </c>
@@ -5911,7 +5908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
         <v>4</v>
       </c>
@@ -5949,7 +5946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
         <v>4</v>
       </c>
@@ -5987,7 +5984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="n">
         <v>4</v>
       </c>
@@ -6025,7 +6022,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="n">
         <v>4</v>
       </c>
@@ -6063,7 +6060,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="n">
         <v>4</v>
       </c>
@@ -6101,7 +6098,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="n">
         <v>4</v>
       </c>
@@ -6139,7 +6136,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="n">
         <v>4</v>
       </c>
@@ -6177,7 +6174,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="n">
         <v>4</v>
       </c>
@@ -6215,7 +6212,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="n">
         <v>4</v>
       </c>
@@ -6253,7 +6250,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="n">
         <v>4</v>
       </c>
@@ -6291,7 +6288,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="n">
         <v>4</v>
       </c>
@@ -6329,7 +6326,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="n">
         <v>4</v>
       </c>
@@ -6367,7 +6364,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="n">
         <v>4</v>
       </c>
@@ -6405,7 +6402,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="n">
         <v>4</v>
       </c>
@@ -6443,7 +6440,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="n">
         <v>4</v>
       </c>
@@ -6481,7 +6478,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="n">
         <v>4</v>
       </c>
@@ -6519,7 +6516,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="n">
         <v>4</v>
       </c>
@@ -6557,7 +6554,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="n">
         <v>4</v>
       </c>
@@ -6595,7 +6592,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="n">
         <v>4</v>
       </c>
@@ -6633,7 +6630,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="n">
         <v>4</v>
       </c>
@@ -6671,7 +6668,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="n">
         <v>4</v>
       </c>
@@ -6709,7 +6706,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="n">
         <v>4</v>
       </c>
@@ -6747,7 +6744,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="n">
         <v>4</v>
       </c>
@@ -6785,7 +6782,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="n">
         <v>4</v>
       </c>
@@ -6858,10 +6855,10 @@
         <v>4</v>
       </c>
       <c r="L160" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="n">
         <v>4</v>
       </c>
@@ -6896,10 +6893,10 @@
         <v>0</v>
       </c>
       <c r="L161" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="n">
         <v>4</v>
       </c>
@@ -6937,7 +6934,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="n">
         <v>4</v>
       </c>
@@ -6975,7 +6972,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="n">
         <v>4</v>
       </c>
@@ -7010,10 +7007,10 @@
         <v>3</v>
       </c>
       <c r="L164" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="n">
         <v>4</v>
       </c>
@@ -7048,10 +7045,10 @@
         <v>3</v>
       </c>
       <c r="L165" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="n">
         <v>4</v>
       </c>
@@ -7089,7 +7086,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="n">
         <v>4</v>
       </c>
@@ -7127,8 +7124,654 @@
         <v>92</v>
       </c>
     </row>
+    <row r="168" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="169" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="170" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="171" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="172" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="173" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="174" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="175" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="176" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="177" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="178" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="179" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="180" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="181" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="182" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="183" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="184" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="185" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="186" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="187" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="188" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="189" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="190" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="191" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="192" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="193" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="194" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="195" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="196" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="197" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="198" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="199" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="200" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="201" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="202" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="203" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="204" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="205" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="206" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="207" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:L806"/>
+  <autoFilter ref="A1:L806">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="PABLO MARIA DEL MORAL JIMENEZ"/>
+        <filter val="PABLO MARIA DEL MORAL JIMENEZ "/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -15986,7 +16629,7 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/PasseD_26_27.xlsx
+++ b/PasseD_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="PASSE D D1 " sheetId="1" state="visible" r:id="rId3"/>
@@ -14351,7 +14351,7 @@
         <v>4</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -16561,7 +16561,7 @@
         <v>4</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
@@ -16610,7 +16610,7 @@
         <v>5</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1"/>
@@ -16659,7 +16659,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="M21" s="2"/>
       <c r="N21" s="1"/>
@@ -19397,7 +19397,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>

--- a/PasseD_26_27.xlsx
+++ b/PasseD_26_27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="PASSE D D1 " sheetId="1" state="visible" r:id="rId3"/>
@@ -720,10 +720,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W206"/>
+  <dimension ref="A1:W806"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.42"/>
@@ -787,7 +787,7 @@
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -836,7 +836,7 @@
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -885,7 +885,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
@@ -934,7 +934,7 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>1</v>
       </c>
@@ -983,7 +983,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>1</v>
       </c>
@@ -1021,7 +1021,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>1</v>
       </c>
@@ -1059,7 +1059,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>1</v>
       </c>
@@ -1097,7 +1097,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>1</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>1</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>1</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>1</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>1</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>1</v>
       </c>
@@ -1363,7 +1363,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>1</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>1</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>1</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>1</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>1</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>1</v>
       </c>
@@ -1591,7 +1591,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>1</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>1</v>
       </c>
@@ -1667,7 +1667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>1</v>
       </c>
@@ -1705,7 +1705,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>1</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>1</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>1</v>
       </c>
@@ -1819,7 +1819,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>1</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>1</v>
       </c>
@@ -1895,7 +1895,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>1</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>1</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>1</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>1</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>1</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>1</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>1</v>
       </c>
@@ -2161,7 +2161,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>1</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>1</v>
       </c>
@@ -2237,7 +2237,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>1</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>1</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>1</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>1</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>1</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
         <v>1</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>1</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>1</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>2</v>
       </c>
@@ -2579,7 +2579,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
         <v>2</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
         <v>2</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
         <v>2</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
         <v>2</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
         <v>2</v>
       </c>
@@ -2769,7 +2769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
         <v>2</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
         <v>2</v>
       </c>
@@ -2845,7 +2845,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
         <v>2</v>
       </c>
@@ -2883,7 +2883,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
         <v>2</v>
       </c>
@@ -2921,7 +2921,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
         <v>2</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
         <v>2</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="n">
         <v>2</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
         <v>2</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
         <v>2</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
         <v>2</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
         <v>2</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
         <v>2</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="n">
         <v>2</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" s="6" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" s="6" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
         <v>2</v>
       </c>
@@ -3312,7 +3312,7 @@
       <c r="V66" s="1"/>
       <c r="W66" s="1"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
         <v>2</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
         <v>2</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
         <v>2</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
         <v>2</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
         <v>2</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="n">
         <v>2</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="n">
         <v>2</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
         <v>2</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
         <v>2</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
         <v>3</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
         <v>3</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
         <v>3</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="n">
         <v>3</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
         <v>3</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
         <v>3</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
         <v>3</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="n">
         <v>3</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="n">
         <v>3</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
         <v>3</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
         <v>3</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
         <v>3</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="n">
         <v>3</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="n">
         <v>3</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="n">
         <v>3</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="n">
         <v>3</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="n">
         <v>3</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="n">
         <v>3</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="n">
         <v>3</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="n">
         <v>3</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="n">
         <v>3</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="n">
         <v>3</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="n">
         <v>3</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="n">
         <v>3</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="n">
         <v>3</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="n">
         <v>3</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="n">
         <v>3</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="n">
         <v>3</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="n">
         <v>3</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="n">
         <v>3</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
         <v>3</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="n">
         <v>3</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="n">
         <v>3</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="n">
         <v>3</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="n">
         <v>3</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="n">
         <v>3</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="n">
         <v>3</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="n">
         <v>3</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="n">
         <v>3</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="n">
         <v>3</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="n">
         <v>3</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="n">
         <v>3</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="n">
         <v>3</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="n">
         <v>3</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="n">
         <v>3</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="n">
         <v>3</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="n">
         <v>3</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="n">
         <v>3</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="n">
         <v>3</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="n">
         <v>3</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="n">
         <v>3</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="n">
         <v>3</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" s="6" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="128" s="6" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="n">
         <v>3</v>
       </c>
@@ -5679,7 +5679,7 @@
       <c r="V128" s="1"/>
       <c r="W128" s="1"/>
     </row>
-    <row r="129" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="n">
         <v>4</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="130" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="n">
         <v>4</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="131" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="n">
         <v>4</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="n">
         <v>4</v>
       </c>
@@ -5842,7 +5842,7 @@
       <c r="V132" s="4"/>
       <c r="W132" s="4"/>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="n">
         <v>4</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="n">
         <v>4</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="n">
         <v>4</v>
       </c>
@@ -5956,7 +5956,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
         <v>4</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
         <v>4</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="n">
         <v>4</v>
       </c>
@@ -6070,7 +6070,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="n">
         <v>4</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="n">
         <v>4</v>
       </c>
@@ -6146,7 +6146,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="n">
         <v>4</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="n">
         <v>4</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="n">
         <v>4</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="n">
         <v>4</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="n">
         <v>4</v>
       </c>
@@ -6336,7 +6336,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="n">
         <v>4</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="n">
         <v>4</v>
       </c>
@@ -6602,7 +6602,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="n">
         <v>4</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="n">
         <v>4</v>
       </c>
@@ -6678,7 +6678,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="n">
         <v>4</v>
       </c>
@@ -6716,7 +6716,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="n">
         <v>4</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="n">
         <v>4</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="n">
         <v>4</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="n">
         <v>4</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="n">
         <v>4</v>
       </c>
@@ -6906,7 +6906,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="n">
         <v>4</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="n">
         <v>4</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="n">
         <v>4</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="n">
         <v>4</v>
       </c>
@@ -7058,7 +7058,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="n">
         <v>4</v>
       </c>
@@ -7096,7 +7096,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="n">
         <v>4</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="n">
         <v>4</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="n">
         <v>5</v>
       </c>
@@ -7207,7 +7207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="n">
         <v>5</v>
       </c>
@@ -7242,7 +7242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="n">
         <v>5</v>
       </c>
@@ -7277,7 +7277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="n">
         <v>5</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="n">
         <v>5</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="n">
         <v>5</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="n">
         <v>5</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="n">
         <v>5</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="n">
         <v>5</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="n">
         <v>5</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="n">
         <v>5</v>
       </c>
@@ -7557,7 +7557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="n">
         <v>5</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="n">
         <v>5</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="n">
         <v>5</v>
       </c>
@@ -7662,7 +7662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="n">
         <v>5</v>
       </c>
@@ -7697,7 +7697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="n">
         <v>5</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="n">
         <v>5</v>
       </c>
@@ -7767,7 +7767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="n">
         <v>5</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="n">
         <v>5</v>
       </c>
@@ -7837,7 +7837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="n">
         <v>5</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="n">
         <v>5</v>
       </c>
@@ -7907,7 +7907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="n">
         <v>5</v>
       </c>
@@ -7942,7 +7942,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="n">
         <v>5</v>
       </c>
@@ -7977,7 +7977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="n">
         <v>5</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="1" t="n">
         <v>5</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="n">
         <v>5</v>
       </c>
@@ -8082,7 +8082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="n">
         <v>5</v>
       </c>
@@ -8117,7 +8117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="n">
         <v>5</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="n">
         <v>5</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="1" t="n">
         <v>5</v>
       </c>
@@ -8222,7 +8222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="1" t="n">
         <v>5</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="n">
         <v>5</v>
       </c>
@@ -8292,7 +8292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="n">
         <v>5</v>
       </c>
@@ -8327,7 +8327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="n">
         <v>5</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="1" t="n">
         <v>5</v>
       </c>
@@ -8397,7 +8397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="1" t="n">
         <v>5</v>
       </c>
@@ -8432,7 +8432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="1" t="n">
         <v>5</v>
       </c>
@@ -8467,7 +8467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="1" t="n">
         <v>5</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="1" t="n">
         <v>5</v>
       </c>
@@ -8537,8 +8537,619 @@
         <v>0</v>
       </c>
     </row>
+    <row r="207" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="208" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="209" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="210" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="211" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="212" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="213" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="214" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="215" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="216" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="217" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="218" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="219" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="220" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="221" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="222" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="223" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="224" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="225" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="226" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="227" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="228" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="229" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="230" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="231" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="232" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="233" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="234" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="235" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="236" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="237" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="238" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="239" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="240" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="241" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="242" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="243" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="244" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="245" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="246" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="247" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="248" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="249" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="250" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="251" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="252" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="253" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="254" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="255" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="256" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="257" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="258" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="259" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="260" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="261" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="262" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="263" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="264" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="265" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="266" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="267" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="268" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="269" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="270" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="271" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="272" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="273" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="274" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="275" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="276" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="277" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="278" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="279" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="280" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="281" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="282" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="283" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="284" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="285" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="286" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="287" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="288" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="289" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="290" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="291" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="292" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="293" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="294" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="295" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="296" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="297" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="298" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="299" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="300" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="301" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="302" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="303" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="304" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="305" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="306" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="307" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="308" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="309" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="310" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="311" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="312" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="313" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="314" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="315" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="316" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="317" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="318" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="319" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="320" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="321" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="322" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="323" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="324" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="325" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="326" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="327" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="328" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="329" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="330" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="331" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="332" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="333" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="334" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="335" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="336" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="337" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="338" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="339" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="340" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="341" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="342" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="343" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="344" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="345" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="346" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="347" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="348" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="349" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="350" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="351" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="352" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="353" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="354" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="355" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="356" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="357" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="358" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="359" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="360" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="361" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="362" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="363" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="364" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="365" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="366" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="367" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="368" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="369" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="370" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="371" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="372" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="373" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="374" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="375" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="376" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="377" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="378" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="379" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="380" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="381" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="382" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="383" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="384" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="385" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="386" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="387" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="388" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="389" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="390" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="391" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="392" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="393" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="394" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="395" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="396" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="397" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="398" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="399" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="400" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="401" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="402" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="403" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="404" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="405" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="406" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="407" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="408" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="409" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="410" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="411" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="412" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="413" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="414" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="415" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="416" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="417" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="418" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="419" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="420" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="421" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="422" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="423" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="424" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="425" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="426" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="427" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="428" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="429" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="430" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="431" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="432" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="433" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="434" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="435" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="436" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="437" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="438" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="439" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="440" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="441" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="442" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="443" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="444" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="445" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="446" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="447" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="448" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="449" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="450" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="451" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="452" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="453" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="454" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="455" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="456" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="457" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="458" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="459" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="460" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="461" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="462" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="463" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="464" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="465" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="466" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="467" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="468" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="469" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="470" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="471" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="472" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="473" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="474" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="475" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="476" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="477" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="478" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="479" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="480" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="481" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="482" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="483" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="484" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="485" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="486" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="487" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="488" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="489" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="490" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="491" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="492" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="493" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="494" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="495" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="496" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="497" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="498" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="499" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="500" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="501" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="502" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="503" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="504" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="505" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="506" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="507" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="508" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="509" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="510" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="511" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="512" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="513" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="514" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="515" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="516" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="517" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="518" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="519" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="520" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="521" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="522" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="523" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="524" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="525" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="526" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="527" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="528" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="529" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="530" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="531" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="532" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="533" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="534" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="535" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="536" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="537" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="538" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="539" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="540" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="541" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="542" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="543" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="544" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="545" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="546" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="547" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="548" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="549" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="550" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="551" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="552" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="553" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="554" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="555" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="556" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="557" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="558" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="559" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="560" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="561" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="562" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="563" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="564" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="565" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="566" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="567" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="568" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="569" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="570" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="571" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="572" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="573" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="574" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="575" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="576" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="577" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="578" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="579" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="580" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="581" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="582" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="583" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="584" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="585" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="586" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="587" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="588" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="589" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="590" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="591" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="592" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="593" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="594" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="595" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="596" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="597" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="598" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="599" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="600" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="601" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="602" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="603" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="604" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="605" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="606" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="607" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="608" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="609" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="610" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="611" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="612" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="613" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="614" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="615" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="616" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="617" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="618" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="619" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="620" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="621" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="622" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="623" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="624" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="625" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="626" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="627" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="628" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="629" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="630" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="631" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="632" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="633" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="634" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="635" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="636" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="637" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="638" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="639" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="640" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="641" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="642" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="643" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="644" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="645" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="646" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="647" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="648" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="649" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="650" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="651" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="652" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="653" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="654" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="655" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="656" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="657" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="658" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="659" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="660" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="661" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="662" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="663" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="664" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="665" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="666" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="667" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="668" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="669" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="670" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="671" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="672" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="673" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="674" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="675" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="676" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="677" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="678" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="679" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="680" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="681" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="682" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="683" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="684" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="685" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="686" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="687" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="688" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="689" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="690" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="691" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="692" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="693" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="694" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="695" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="696" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="697" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="698" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="699" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="700" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="701" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="702" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="703" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="704" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="705" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="706" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="707" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="708" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="709" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="710" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="711" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="712" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="713" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="714" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="715" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="716" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="717" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="718" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="719" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="720" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="721" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="722" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="723" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="724" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="725" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="726" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="727" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="728" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="729" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="730" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="731" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="732" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="733" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="734" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="735" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="736" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="737" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="738" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="739" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="740" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="741" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="742" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="743" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="744" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="745" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="746" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="747" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="748" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="749" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="750" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="751" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="752" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="753" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="754" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="755" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="756" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="757" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="758" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="759" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="760" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="761" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="762" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="763" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="764" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="765" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="766" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="767" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="768" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="769" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="770" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="771" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="772" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="773" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="774" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="775" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="776" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="777" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="778" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="779" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="780" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="781" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="782" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="783" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="784" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="785" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="786" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="787" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="788" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="789" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="790" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="791" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="792" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="793" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="794" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="795" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="796" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="797" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="798" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="799" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="800" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="801" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="802" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="803" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="804" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="805" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="806" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:L806"/>
+  <autoFilter ref="A1:L806">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="4"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="1">
+      <filters>
+        <filter val="UJS TOULOUSE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
